--- a/resources/reselling/files/reselling-int-weekly-log.xlsx
+++ b/resources/reselling/files/reselling-int-weekly-log.xlsx
@@ -139,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -171,12 +171,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -546,7 +540,7 @@
   <dimension ref="A1:AA38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -589,7 +583,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -629,7 +622,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="63" customHeight="1">
+    <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Week ending</t>
@@ -766,7 +759,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="63" customHeight="1">
+    <row r="10">
       <c r="A10" s="7" t="n"/>
       <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
@@ -825,7 +818,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="63" customHeight="1">
+    <row r="11">
       <c r="A11" s="7" t="n"/>
       <c r="B11" s="8" t="n"/>
       <c r="C11" s="8" t="n"/>
@@ -884,7 +877,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="63" customHeight="1">
+    <row r="12">
       <c r="A12" s="7" t="n"/>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
@@ -943,7 +936,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="63" customHeight="1">
+    <row r="13">
       <c r="A13" s="7" t="n"/>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
@@ -1002,7 +995,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="63" customHeight="1">
+    <row r="14">
       <c r="A14" s="7" t="n"/>
       <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
@@ -1061,7 +1054,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="63" customHeight="1">
+    <row r="15">
       <c r="A15" s="7" t="n"/>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
@@ -1120,7 +1113,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="63" customHeight="1">
+    <row r="16">
       <c r="A16" s="7" t="n"/>
       <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
@@ -1179,7 +1172,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="63" customHeight="1">
+    <row r="17">
       <c r="A17" s="7" t="n"/>
       <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
@@ -1238,7 +1231,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="63" customHeight="1">
+    <row r="18">
       <c r="A18" s="7" t="n"/>
       <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
@@ -1297,7 +1290,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="63" customHeight="1">
+    <row r="19">
       <c r="A19" s="7" t="n"/>
       <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
@@ -1356,7 +1349,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="63" customHeight="1">
+    <row r="20">
       <c r="A20" s="7" t="n"/>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
@@ -1415,7 +1408,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="63" customHeight="1">
+    <row r="21">
       <c r="A21" s="7" t="n"/>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
@@ -1474,7 +1467,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="63" customHeight="1">
+    <row r="22">
       <c r="A22" s="7" t="n"/>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
@@ -1533,7 +1526,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="63" customHeight="1">
+    <row r="23">
       <c r="A23" s="7" t="n"/>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
@@ -1592,7 +1585,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="63" customHeight="1">
+    <row r="24">
       <c r="A24" s="7" t="n"/>
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
@@ -1651,7 +1644,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="63" customHeight="1">
+    <row r="25">
       <c r="A25" s="7" t="n"/>
       <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
@@ -1710,7 +1703,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="63" customHeight="1">
+    <row r="26">
       <c r="A26" s="7" t="n"/>
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
@@ -1769,7 +1762,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="63" customHeight="1">
+    <row r="27">
       <c r="A27" s="7" t="n"/>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
@@ -1828,7 +1821,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="63" customHeight="1">
+    <row r="28">
       <c r="A28" s="7" t="n"/>
       <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
@@ -1887,7 +1880,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="63" customHeight="1">
+    <row r="29">
       <c r="A29" s="7" t="n"/>
       <c r="B29" s="8" t="n"/>
       <c r="C29" s="8" t="n"/>
@@ -1946,7 +1939,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="63" customHeight="1">
+    <row r="30">
       <c r="A30" s="7" t="n"/>
       <c r="B30" s="8" t="n"/>
       <c r="C30" s="8" t="n"/>
@@ -2005,7 +1998,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="63" customHeight="1">
+    <row r="31">
       <c r="A31" s="7" t="n"/>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
@@ -2064,7 +2057,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" ht="63" customHeight="1">
+    <row r="32">
       <c r="A32" s="7" t="n"/>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
@@ -2123,7 +2116,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" ht="63" customHeight="1">
+    <row r="33">
       <c r="A33" s="7" t="n"/>
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
@@ -2182,7 +2175,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="63" customHeight="1">
+    <row r="34">
       <c r="A34" s="7" t="n"/>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
@@ -2241,7 +2234,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="63" customHeight="1">
+    <row r="35">
       <c r="A35" s="7" t="n"/>
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
@@ -2319,11 +2312,10 @@
         <v/>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global  ·  The Reselling shelf: Basics · Intermediate · Advanced — eports.global/resources/reselling</t>
+          <t>ePORTS — your ecom source (eports.global)  ·  The Reselling shelf: Basics · Intermediate · Advanced — eports.global/resources/reselling</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2333,7 @@
   <dimension ref="A1:AA16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -2370,8 +2362,8 @@
     <col width="11" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Weekly log + open-to-buy (Reselling — Intermediate, ch4/5/10)  —  EXAMPLE: Terri's four weeks from the book</t>
         </is>
@@ -2384,7 +2376,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2432,7 +2423,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="63" customHeight="1">
+    <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Week ending</t>
@@ -2569,7 +2560,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="63" customHeight="1">
+    <row r="10">
       <c r="A10" s="7" t="n">
         <v>46271</v>
       </c>
@@ -2639,7 +2630,7 @@
         <f>IF(OR(T10="",NOT(ISNUMBER(O10))),"",IF(O10=0,"",T10/O10))</f>
         <v/>
       </c>
-      <c r="V10" s="17" t="inlineStr">
+      <c r="V10" s="8" t="inlineStr">
         <is>
           <t>Sunday ran to 2¾ — skeleton built</t>
         </is>
@@ -2662,7 +2653,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="63" customHeight="1">
+    <row r="11">
       <c r="A11" s="7" t="n">
         <v>46278</v>
       </c>
@@ -2734,7 +2725,7 @@
         <f>IF(OR(T11="",NOT(ISNUMBER(O11))),"",IF(O11=0,"",T11/O11))</f>
         <v/>
       </c>
-      <c r="V11" s="17" t="inlineStr">
+      <c r="V11" s="8" t="inlineStr">
         <is>
           <t>aging report + liquidation protocol built</t>
         </is>
@@ -2757,7 +2748,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="63" customHeight="1">
+    <row r="12">
       <c r="A12" s="7" t="n">
         <v>46285</v>
       </c>
@@ -2829,7 +2820,7 @@
         <f>IF(OR(T12="",NOT(ISNUMBER(O12))),"",IF(O12=0,"",T12/O12))</f>
         <v/>
       </c>
-      <c r="V12" s="17" t="inlineStr">
+      <c r="V12" s="8" t="inlineStr">
         <is>
           <t>cash received $96 → $164; net −$160 → −$92; added at audit, 27 Sept</t>
         </is>
@@ -2852,7 +2843,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="63" customHeight="1">
+    <row r="13">
       <c r="A13" s="7" t="n">
         <v>46292</v>
       </c>
@@ -2924,7 +2915,7 @@
         <f>IF(OR(T13="",NOT(ISNUMBER(O13))),"",IF(O13=0,"",T13/O13))</f>
         <v/>
       </c>
-      <c r="V13" s="17" t="inlineStr">
+      <c r="V13" s="8" t="inlineStr">
         <is>
           <t>Mercari batch running; read 18 Oct</t>
         </is>
@@ -2966,11 +2957,10 @@
         <v/>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global  ·  The Reselling shelf: Basics · Intermediate · Advanced — eports.global/resources/reselling</t>
+          <t>ePORTS — your ecom source (eports.global)  ·  The Reselling shelf: Basics · Intermediate · Advanced — eports.global/resources/reselling</t>
         </is>
       </c>
     </row>
